--- a/src/evaluation/data/scraping_stats_Advanced_NoTechniques.xlsx
+++ b/src/evaluation/data/scraping_stats_Advanced_NoTechniques.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45960</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1453.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="13">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39.29</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="15">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2357</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.13</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="17">
@@ -604,7 +604,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-01-21 12:38:00</t>
+          <t>2026-01-21 14:32:11</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-01-21 13:17:17</t>
+          <t>2026-01-21 14:34:11</t>
         </is>
       </c>
     </row>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45960</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,343 +751,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gesamt Chunks</t>
+          <t>Keine Daten</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45960</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Minimum (Zeichen)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Maximum (Zeichen)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Durchschnitt (Zeichen)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1453.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Median (Zeichen)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Std. Abweichung (Zeichen)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>203.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Perzentil 10%</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Perzentil 25%</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Perzentil 50%</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Perzentil 75%</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Perzentil 90%</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Perzentil 95%</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Perzentil 99%</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Bereich (Zeichen)</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Anzahl</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>Anteil (%)</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>0-200</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>262</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>200-400</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>330</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>400-600</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>493</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>600-800</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>424</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>800-1000</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>467</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1000-1200</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>427</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1200-1400</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>421</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1400-1600</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>43136</v>
-      </c>
-      <c r="C25" t="n">
-        <v>93.90000000000001</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1600-1800</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1800-2000</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2000-2500</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2500-3000</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>3000-5000</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>5000-10000</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>&gt;10000</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1101,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,343 +804,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gesamt Chunks</t>
+          <t>Keine Daten</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45960</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Minimum (Tokens)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Maximum (Tokens)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Durchschnitt (Tokens)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>320.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Median (Tokens)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Std. Abweichung (Tokens)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>54.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Perzentil 10%</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Perzentil 25%</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Perzentil 50%</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Perzentil 75%</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Perzentil 90%</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Perzentil 95%</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Perzentil 99%</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Bereich (Tokens)</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Anzahl</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>Anteil (%)</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>0-50</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>276</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>50-100</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>377</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>100-150</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>534</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>150-200</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>621</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>200-250</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>763</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>250-300</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>6832</v>
-      </c>
-      <c r="C23" t="n">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>300-350</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>27199</v>
-      </c>
-      <c r="C24" t="n">
-        <v>59.2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>350-400</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>7879</v>
-      </c>
-      <c r="C25" t="n">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>400-450</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1136</v>
-      </c>
-      <c r="C26" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>450-500</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>313</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>500-600</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>600-700</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>700-800</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>800-1000</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>&gt;1000</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
